--- a/docs/downloads/09/t11_sources_emprunt_alaotra_tous.xlsx
+++ b/docs/downloads/09/t11_sources_emprunt_alaotra_tous.xlsx
@@ -387,12 +387,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -405,12 +399,6 @@
           <t>Commerçants</t>
         </is>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -441,12 +429,6 @@
           <t>Usuriers</t>
         </is>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -459,12 +441,6 @@
           <t>Voisins</t>
         </is>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>25</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -477,12 +453,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -531,12 +501,6 @@
           <t>Usuriers</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>2.9</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -567,12 +531,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -621,12 +579,6 @@
           <t>Usuriers</t>
         </is>
       </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -657,12 +609,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -711,12 +657,6 @@
           <t>Usuriers</t>
         </is>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -747,12 +687,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>6.7</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -765,12 +699,6 @@
           <t>Commerçants</t>
         </is>
       </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="D23">
-        <v>13.3</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -801,12 +729,6 @@
           <t>Usuriers</t>
         </is>
       </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>6.7</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -837,12 +759,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C27">
-        <v>2</v>
-      </c>
-      <c r="D27">
-        <v>6.7</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -855,12 +771,6 @@
           <t>Commerçants</t>
         </is>
       </c>
-      <c r="C28">
-        <v>4</v>
-      </c>
-      <c r="D28">
-        <v>12.1</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -891,12 +801,6 @@
           <t>Usuriers</t>
         </is>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -927,12 +831,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -981,12 +879,6 @@
           <t>Usuriers</t>
         </is>
       </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1017,12 +909,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>2.7</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1071,12 +957,6 @@
           <t>Usuriers</t>
         </is>
       </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
-        <v>2.7</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1107,12 +987,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C42">
-        <v>4</v>
-      </c>
-      <c r="D42">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1160,12 +1034,6 @@
         <is>
           <t>Usuriers</t>
         </is>
-      </c>
-      <c r="C45">
-        <v>4</v>
-      </c>
-      <c r="D45">
-        <v>1.7</v>
       </c>
     </row>
     <row r="46">

--- a/docs/downloads/09/t11_sources_emprunt_alaotra_tous.xlsx
+++ b/docs/downloads/09/t11_sources_emprunt_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -391,7 +391,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -403,7 +403,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -421,7 +421,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -457,7 +457,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -763,7 +763,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -949,7 +949,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1009,7 +1009,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
